--- a/data/test_strategic.xlsx
+++ b/data/test_strategic.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>Automation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -504,15 +504,101 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
+          <t>$100k - $500k</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>watsonx Orchestrate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>&gt; $500k</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K2" t="b">
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hashicorp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>&lt; $100k</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/test_strategic.xlsx
+++ b/data/test_strategic.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -581,11 +581,7 @@
           <t>&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
@@ -593,11 +589,7 @@
           <t>&lt; $100k</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="b">
         <v>1</v>
       </c>

--- a/data/test_strategic.xlsx
+++ b/data/test_strategic.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Verify</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>automation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -495,11 +495,7 @@
           <t>&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
@@ -529,7 +525,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -538,11 +534,7 @@
           <t>&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
@@ -552,11 +544,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -591,6 +583,49 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AI on-prem</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>&gt; $500k</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
         <v>1</v>
       </c>
     </row>
